--- a/src/nodes/P/compresor_blade_self_frequency.xlsx
+++ b/src/nodes/P/compresor_blade_self_frequency.xlsx
@@ -552,58 +552,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>49.616138002389782</v>
+        <v>40.521436948085061</v>
       </c>
       <c r="C3">
-        <v>310.9614718493649</v>
+        <v>253.96183947692293</v>
       </c>
       <c r="D3">
-        <v>870.78871361106553</v>
+        <v>711.17203745272047</v>
       </c>
       <c r="E3">
-        <v>1707.6772119578068</v>
+        <v>1394.6578121154255</v>
       </c>
       <c r="F3">
-        <v>2821.754534611232</v>
+        <v>2304.5233478614327</v>
       </c>
       <c r="G3">
-        <v>4214.1296132815041</v>
+        <v>3441.674307811295</v>
       </c>
       <c r="H3">
-        <v>289.79952600105696</v>
+        <v>224.76511671652992</v>
       </c>
       <c r="I3">
-        <v>869.39857800317088</v>
+        <v>674.29535014958969</v>
       </c>
       <c r="J3">
-        <v>1448.9976300052847</v>
+        <v>1123.8255835826494</v>
       </c>
       <c r="K3">
-        <v>2028.5966820073988</v>
+        <v>1573.3558170157094</v>
       </c>
       <c r="L3">
-        <v>2608.1957340095123</v>
+        <v>2022.8860504487689</v>
       </c>
       <c r="M3">
-        <v>3187.7947860116265</v>
+        <v>2472.4162838818288</v>
       </c>
       <c r="N3">
-        <v>579.59905200211392</v>
+        <v>449.53023343305983</v>
       </c>
       <c r="O3">
-        <v>1159.1981040042278</v>
+        <v>899.06046686611967</v>
       </c>
       <c r="P3">
-        <v>1738.7971560063418</v>
+        <v>1348.5907002991794</v>
       </c>
       <c r="Q3">
-        <v>2318.3962080084557</v>
+        <v>1798.1209337322393</v>
       </c>
       <c r="R3">
-        <v>2897.9952600105694</v>
+        <v>2247.6511671652988</v>
       </c>
       <c r="S3">
-        <v>3477.5943120126835</v>
+        <v>2697.1814005983588</v>
       </c>
     </row>
   </sheetData>
